--- a/Datas/StoreCounterDataList.xlsx
+++ b/Datas/StoreCounterDataList.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>counterName</t>
   </si>
@@ -95,7 +95,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0,1,3,4,5,6</t>
+    <t>0,0.08,-0.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,3,4,5,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0.08,-0.11</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -485,7 +493,7 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -496,7 +504,7 @@
         <v>301</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -510,7 +518,10 @@
         <v>302</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/StoreCounterDataList.xlsx
+++ b/Datas/StoreCounterDataList.xlsx
@@ -91,10 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0,0.24,-0.12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0,0.08,-0.12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -104,6 +100,10 @@
   </si>
   <si>
     <t>0,0.08,-0.11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0.24,-0.24</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,10 +490,10 @@
         <v>300</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -504,7 +504,7 @@
         <v>301</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -518,7 +518,7 @@
         <v>302</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>1</v>

--- a/Datas/StoreCounterDataList.xlsx
+++ b/Datas/StoreCounterDataList.xlsx
@@ -487,7 +487,7 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -501,7 +501,7 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>301</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -515,7 +515,7 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>302</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>

--- a/Datas/StoreCounterDataList.xlsx
+++ b/Datas/StoreCounterDataList.xlsx
@@ -95,15 +95,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0,3,4,5,6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0,0.08,-0.11</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>0,0.24,-0.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,3,4,5,6,12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,10 +490,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -518,7 +518,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>1</v>
